--- a/public/excel/product/Giá thép hộp đen cỡ lớn.xlsx
+++ b/public/excel/product/Giá thép hộp đen cỡ lớn.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="476">
   <si>
     <t xml:space="preserve">Tên</t>
   </si>
@@ -58,6 +58,9 @@
     <t xml:space="preserve">Loại</t>
   </si>
   <si>
+    <t xml:space="preserve">Lô hàng</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hộp đen 300 x 300 x 8</t>
   </si>
   <si>
@@ -73,6 +76,9 @@
     <t xml:space="preserve">Thép hình</t>
   </si>
   <si>
+    <t xml:space="preserve">ISM221</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hộp đen 350 x 350 x 10</t>
   </si>
   <si>
@@ -211,6 +217,9 @@
     <t xml:space="preserve">Thép hộp đen 100 x 150 x 2.0 x 6m</t>
   </si>
   <si>
+    <t xml:space="preserve">ISM222</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thép hộp đen 100 x 150 x 2.5 x 6m</t>
   </si>
   <si>
@@ -353,6 +362,9 @@
   </si>
   <si>
     <t xml:space="preserve">Thép hộp đen 100 x 200 x 3.0 x 6m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISM223</t>
   </si>
   <si>
     <t xml:space="preserve">Thép hộp đen 100 x 200 x 3.2 x 6m</t>
@@ -1712,7 +1724,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="33.57"/>
@@ -1749,10 +1761,13 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>6</v>
@@ -1764,24 +1779,27 @@
         <v>11.818</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>13</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="7" t="n">
         <v>6</v>
@@ -1793,24 +1811,27 @@
         <v>19.091</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" s="8" t="n">
         <v>21</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>6</v>
@@ -1822,24 +1843,27 @@
         <v>19.091</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>6</v>
@@ -1851,24 +1875,27 @@
         <v>19.091</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>6</v>
@@ -1880,24 +1907,27 @@
         <v>19.091</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>6</v>
@@ -1909,24 +1939,27 @@
         <v>19.091</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>6</v>
@@ -1938,24 +1971,27 @@
         <v>19.091</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>6</v>
@@ -1967,24 +2003,27 @@
         <v>19.091</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>6</v>
@@ -1996,24 +2035,27 @@
         <v>19.091</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>6</v>
@@ -2025,24 +2067,27 @@
         <v>19.091</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>6</v>
@@ -2054,24 +2099,27 @@
         <v>19.091</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>6</v>
@@ -2092,15 +2140,18 @@
         <v>478.133</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>6</v>
@@ -2121,15 +2172,18 @@
         <v>822.438</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>6</v>
@@ -2150,15 +2204,18 @@
         <v>917.66</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>6</v>
@@ -2179,15 +2236,18 @@
         <v>980.842</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>6</v>
@@ -2205,18 +2265,21 @@
         <v>18</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>6</v>
@@ -2228,24 +2291,27 @@
         <v>16.364</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>18</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>6</v>
@@ -2257,24 +2323,27 @@
         <v>16.364</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>18</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>6</v>
@@ -2286,24 +2355,27 @@
         <v>16.364</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>18</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>6</v>
@@ -2324,15 +2396,18 @@
         <v>884.725</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>6</v>
@@ -2344,24 +2419,27 @@
         <v>17.409</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>6</v>
@@ -2373,24 +2451,27 @@
         <v>17.409</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>6</v>
@@ -2402,24 +2483,27 @@
         <v>17.409</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>6</v>
@@ -2431,24 +2515,27 @@
         <v>17.409</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>6</v>
@@ -2460,24 +2547,27 @@
         <v>17.409</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>6</v>
@@ -2489,24 +2579,27 @@
         <v>17.409</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>6</v>
@@ -2518,24 +2611,27 @@
         <v>17.409</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>6</v>
@@ -2553,18 +2649,21 @@
         <v>19.15</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>6</v>
@@ -2576,24 +2675,27 @@
         <v>17.409</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F30" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>6</v>
@@ -2605,24 +2707,27 @@
         <v>17.409</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>6</v>
@@ -2634,24 +2739,27 @@
         <v>17.409</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F32" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>6</v>
@@ -2663,24 +2771,27 @@
         <v>17.409</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F33" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>6</v>
@@ -2692,24 +2803,27 @@
         <v>17.409</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F34" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>6</v>
@@ -2721,24 +2835,27 @@
         <v>17.409</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>6</v>
@@ -2750,24 +2867,27 @@
         <v>17.409</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>6</v>
@@ -2785,18 +2905,21 @@
         <v>19.15</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>6</v>
@@ -2808,24 +2931,27 @@
         <v>17.409</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B39" s="3" t="n">
         <v>6</v>
@@ -2837,24 +2963,27 @@
         <v>17.409</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B40" s="3" t="n">
         <v>6</v>
@@ -2866,24 +2995,27 @@
         <v>17.409</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F40" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B41" s="3" t="n">
         <v>6</v>
@@ -2895,24 +3027,27 @@
         <v>17.409</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F41" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B42" s="3" t="n">
         <v>6</v>
@@ -2924,24 +3059,27 @@
         <v>12.727</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F42" s="4" t="n">
         <v>14</v>
       </c>
       <c r="G42" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J42" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B43" s="3" t="n">
         <v>6</v>
@@ -2953,24 +3091,27 @@
         <v>12.727</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F43" s="4" t="n">
         <v>14</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B44" s="3" t="n">
         <v>6</v>
@@ -2982,19 +3123,22 @@
         <v>12.727</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F44" s="4" t="n">
         <v>14</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -3021,7 +3165,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -3097,7 +3241,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
@@ -3184,7 +3328,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>6</v>
@@ -3271,7 +3415,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>6</v>
@@ -3358,7 +3502,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6</v>
@@ -3445,7 +3589,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>6</v>
@@ -3532,7 +3676,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>6</v>
@@ -3619,7 +3763,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>6</v>
@@ -3706,7 +3850,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>6</v>
@@ -3793,7 +3937,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>6</v>
@@ -3880,7 +4024,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>6</v>
@@ -3967,7 +4111,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>6</v>
@@ -4054,7 +4198,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>6</v>
@@ -4141,7 +4285,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>6</v>
@@ -4228,7 +4372,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>6</v>
@@ -4315,7 +4459,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>6</v>
@@ -4429,7 +4573,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C1" s="7" t="n">
         <v>6</v>
@@ -4456,7 +4600,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
@@ -4483,7 +4627,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>6</v>
@@ -4510,7 +4654,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>6</v>
@@ -4537,7 +4681,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6</v>
@@ -4564,7 +4708,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>6</v>
@@ -4591,7 +4735,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>6</v>
@@ -4618,7 +4762,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>6</v>
@@ -4645,7 +4789,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>6</v>
@@ -4672,7 +4816,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>6</v>
@@ -4699,7 +4843,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>6</v>
@@ -4726,7 +4870,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>6</v>
@@ -4753,7 +4897,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>6</v>
@@ -4780,7 +4924,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>6</v>
@@ -4807,7 +4951,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>6</v>
@@ -4834,7 +4978,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>6</v>
@@ -4861,7 +5005,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>6</v>
@@ -4888,7 +5032,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>6</v>
@@ -4915,7 +5059,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>6</v>
@@ -4942,7 +5086,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>6</v>
@@ -4969,7 +5113,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>6</v>
@@ -4996,7 +5140,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>6</v>
@@ -5023,7 +5167,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>6</v>
@@ -5050,7 +5194,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>6</v>
@@ -5077,7 +5221,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>6</v>
@@ -5104,7 +5248,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>6</v>
@@ -5131,7 +5275,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>6</v>
@@ -5158,7 +5302,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>6</v>
@@ -5185,7 +5329,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>6</v>
@@ -5212,7 +5356,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>6</v>
@@ -5239,7 +5383,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>6</v>
@@ -5266,7 +5410,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>6</v>
@@ -5293,7 +5437,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>6</v>
@@ -5320,7 +5464,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>6</v>
@@ -5347,7 +5491,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>6</v>
@@ -5374,7 +5518,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>6</v>
@@ -5401,7 +5545,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>6</v>
@@ -5428,7 +5572,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>6</v>
@@ -5455,7 +5599,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>6</v>
@@ -5482,7 +5626,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>6</v>
@@ -5509,7 +5653,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>6</v>
@@ -5536,7 +5680,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>6</v>
@@ -5563,7 +5707,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>6</v>
@@ -5590,7 +5734,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>6</v>
@@ -5617,7 +5761,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>6</v>
@@ -5644,7 +5788,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>6</v>
@@ -5671,7 +5815,7 @@
         <v>47</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>6</v>
@@ -5698,7 +5842,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>6</v>
@@ -5725,7 +5869,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>6</v>
@@ -5752,7 +5896,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>6</v>
@@ -5779,7 +5923,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>6</v>
@@ -5806,7 +5950,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>6</v>
@@ -5833,7 +5977,7 @@
         <v>53</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>6</v>
@@ -5860,7 +6004,7 @@
         <v>54</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>6</v>
@@ -5923,7 +6067,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
@@ -5950,7 +6094,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>6</v>
@@ -5977,7 +6121,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>6</v>
@@ -6004,7 +6148,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6</v>
@@ -6031,7 +6175,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>6</v>
@@ -6058,7 +6202,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>6</v>
@@ -6085,7 +6229,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>6</v>
@@ -6112,7 +6256,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>6</v>
@@ -6139,7 +6283,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>6</v>
@@ -6166,7 +6310,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>6</v>
@@ -6193,7 +6337,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>6</v>
@@ -6220,7 +6364,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>6</v>
@@ -6247,7 +6391,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>6</v>
@@ -6274,7 +6418,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>6</v>
@@ -6301,7 +6445,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>6</v>
@@ -6328,7 +6472,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>6</v>
@@ -6355,7 +6499,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>6</v>
@@ -6382,7 +6526,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>6</v>
@@ -6409,7 +6553,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>6</v>
@@ -6436,7 +6580,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>6</v>
@@ -6463,7 +6607,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>6</v>
@@ -6490,7 +6634,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>6</v>
@@ -6517,7 +6661,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>6</v>
@@ -6544,7 +6688,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>6</v>
@@ -6571,7 +6715,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>6</v>
@@ -6598,7 +6742,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>6</v>
@@ -6625,7 +6769,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>6</v>
@@ -6652,7 +6796,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>6</v>
@@ -6679,7 +6823,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>6</v>
@@ -6706,7 +6850,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>6</v>
@@ -6733,7 +6877,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>6</v>
@@ -6760,7 +6904,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C33" s="3" t="n">
         <v>6</v>
@@ -6787,7 +6931,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>6</v>
@@ -6814,7 +6958,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>6</v>
@@ -6841,7 +6985,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>6</v>
@@ -6868,7 +7012,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>6</v>
@@ -6895,7 +7039,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>6</v>
@@ -6922,7 +7066,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>6</v>
@@ -6949,7 +7093,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>6</v>
@@ -6976,7 +7120,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>6</v>
@@ -7003,7 +7147,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>6</v>
@@ -7030,7 +7174,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>6</v>
@@ -7057,7 +7201,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>6</v>
@@ -7084,7 +7228,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>6</v>
@@ -7111,7 +7255,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>6</v>
@@ -7138,7 +7282,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>6</v>
@@ -7165,7 +7309,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>6</v>
@@ -7192,7 +7336,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>6</v>
@@ -7219,7 +7363,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>6</v>
@@ -7246,7 +7390,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>6</v>
@@ -7273,7 +7417,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>6</v>
@@ -7300,7 +7444,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>6</v>
@@ -7327,7 +7471,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>6</v>
@@ -7354,7 +7498,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C55" s="3" t="n">
         <v>6</v>
@@ -7381,7 +7525,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>6</v>
@@ -7408,7 +7552,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>6</v>
@@ -7435,7 +7579,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>6</v>
@@ -7462,7 +7606,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>6</v>
@@ -7489,7 +7633,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>0</v>
@@ -7516,7 +7660,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>6</v>
@@ -7543,7 +7687,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C62" s="3" t="n">
         <v>6</v>
@@ -7570,7 +7714,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>6</v>
@@ -7597,7 +7741,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>6</v>
@@ -7624,7 +7768,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>6</v>
@@ -7651,7 +7795,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>6</v>
@@ -7678,7 +7822,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>6</v>
@@ -7705,7 +7849,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>6</v>
@@ -7732,7 +7876,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>6</v>
@@ -7759,7 +7903,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>6</v>
@@ -7786,7 +7930,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>6</v>
@@ -7813,7 +7957,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>6</v>
@@ -7840,7 +7984,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C73" s="3" t="n">
         <v>6</v>
@@ -7867,7 +8011,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>6</v>
@@ -7894,7 +8038,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>6</v>
@@ -7921,7 +8065,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C76" s="3" t="n">
         <v>6</v>
@@ -7948,7 +8092,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>6</v>
@@ -7975,7 +8119,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>6</v>
@@ -8002,7 +8146,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>6</v>
@@ -8029,7 +8173,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C80" s="3" t="n">
         <v>6</v>
@@ -8056,7 +8200,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>6</v>
@@ -8083,7 +8227,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C82" s="3" t="n">
         <v>6</v>
@@ -8110,7 +8254,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>6</v>
@@ -8137,7 +8281,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>6</v>
@@ -8164,7 +8308,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>6</v>
@@ -8191,7 +8335,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C86" s="3" t="n">
         <v>6</v>
@@ -8218,7 +8362,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>6</v>
@@ -8245,7 +8389,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>6</v>
@@ -8272,7 +8416,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>6</v>
@@ -8299,7 +8443,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C90" s="3" t="n">
         <v>6</v>
@@ -8326,7 +8470,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>6</v>
@@ -8353,7 +8497,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>6</v>
@@ -8380,7 +8524,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>6</v>
@@ -8407,7 +8551,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>6</v>
@@ -8434,7 +8578,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>6</v>
@@ -8461,7 +8605,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>6</v>
@@ -8523,7 +8667,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
@@ -8550,7 +8694,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>8</v>
@@ -8562,13 +8706,13 @@
         <v>11.818</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I3" s="10"/>
     </row>
@@ -8577,7 +8721,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>8</v>
@@ -8589,13 +8733,13 @@
         <v>11.818</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I4" s="10"/>
     </row>
@@ -8604,7 +8748,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>8</v>
@@ -8616,13 +8760,13 @@
         <v>11.818</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="I5" s="10"/>
     </row>
@@ -8631,7 +8775,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>10</v>
@@ -8643,13 +8787,13 @@
         <v>11.818</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="I6" s="10"/>
     </row>
@@ -8658,7 +8802,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>12.5</v>
@@ -8670,13 +8814,13 @@
         <v>11.818</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="I7" s="10"/>
     </row>
@@ -8685,7 +8829,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>12.5</v>
@@ -8697,13 +8841,13 @@
         <v>11.818</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="I8" s="10"/>
     </row>
@@ -8712,7 +8856,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>12</v>
@@ -8724,13 +8868,13 @@
         <v>11.818</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="I9" s="10"/>
     </row>
@@ -8739,7 +8883,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>12</v>
@@ -8751,13 +8895,13 @@
         <v>11.818</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>13</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="I10" s="11"/>
     </row>
@@ -8793,7 +8937,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C1" s="3" t="n">
         <v>6</v>
@@ -8805,13 +8949,13 @@
         <v>15</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G1" s="4" t="n">
         <v>16.5</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="I1" s="10"/>
     </row>
@@ -8820,7 +8964,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
@@ -8832,13 +8976,13 @@
         <v>15</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>16.5</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="I2" s="10"/>
     </row>
@@ -8847,7 +8991,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>6</v>
@@ -8859,13 +9003,13 @@
         <v>15</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>16.5</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I3" s="10"/>
     </row>
@@ -8874,7 +9018,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>6</v>
@@ -8886,13 +9030,13 @@
         <v>15</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>16.5</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="I4" s="10"/>
     </row>
@@ -8901,7 +9045,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6</v>
@@ -8913,13 +9057,13 @@
         <v>15</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>16.5</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I5" s="11"/>
     </row>
@@ -8953,7 +9097,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C1" s="3" t="n">
         <v>6</v>
@@ -8980,7 +9124,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
@@ -9007,7 +9151,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>6</v>
@@ -9034,7 +9178,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>6</v>
@@ -9061,7 +9205,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>6</v>
@@ -9088,7 +9232,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>6</v>
@@ -9115,7 +9259,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>6</v>
@@ -9142,7 +9286,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>6</v>
@@ -9169,7 +9313,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>6</v>
@@ -9196,7 +9340,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>6</v>
@@ -9223,7 +9367,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>6</v>
@@ -9241,7 +9385,7 @@
         <v>13.8</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="I11" s="10"/>
     </row>
@@ -9250,7 +9394,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>6</v>
@@ -9262,13 +9406,13 @@
         <v>12.545</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I12" s="10"/>
     </row>
@@ -9277,7 +9421,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>6</v>
@@ -9289,13 +9433,13 @@
         <v>12.545</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I13" s="10"/>
     </row>
@@ -9304,7 +9448,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>6</v>
@@ -9316,13 +9460,13 @@
         <v>12.545</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="I14" s="10"/>
     </row>
@@ -9331,7 +9475,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>6</v>
@@ -9343,13 +9487,13 @@
         <v>12.545</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="I15" s="10"/>
     </row>
@@ -9358,7 +9502,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>6</v>
@@ -9370,13 +9514,13 @@
         <v>12.545</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="I16" s="10"/>
     </row>
@@ -9385,7 +9529,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>6</v>
@@ -9397,13 +9541,13 @@
         <v>12.545</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="I17" s="10"/>
     </row>
@@ -9412,7 +9556,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>6</v>
@@ -9424,13 +9568,13 @@
         <v>12.545</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="I18" s="10"/>
     </row>
@@ -9439,7 +9583,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>6</v>
@@ -9451,13 +9595,13 @@
         <v>12.545</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I19" s="10"/>
     </row>
@@ -9466,7 +9610,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>6</v>
@@ -9478,13 +9622,13 @@
         <v>12.545</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="I20" s="10"/>
     </row>
@@ -9493,7 +9637,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>6</v>
@@ -9505,13 +9649,13 @@
         <v>12.545</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="I21" s="10"/>
     </row>
@@ -9520,7 +9664,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>6</v>
@@ -9532,13 +9676,13 @@
         <v>12.545</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>13.8</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="I22" s="11"/>
     </row>
@@ -9570,7 +9714,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C1" s="3" t="n">
         <v>6</v>
@@ -9597,7 +9741,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
@@ -9624,7 +9768,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>6</v>
@@ -9651,7 +9795,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>6</v>
@@ -9701,7 +9845,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C1" s="3" t="n">
         <v>6</v>
@@ -9713,13 +9857,13 @@
         <v>27.273</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="G1" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="I1" s="10"/>
     </row>
@@ -9728,7 +9872,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
@@ -9740,13 +9884,13 @@
         <v>27.273</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="I2" s="10"/>
     </row>
@@ -9755,7 +9899,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>6</v>
@@ -9767,13 +9911,13 @@
         <v>27.273</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="I3" s="10"/>
     </row>
@@ -9782,7 +9926,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>6</v>
@@ -9794,13 +9938,13 @@
         <v>27.273</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="I4" s="10"/>
     </row>
@@ -9809,7 +9953,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6</v>
@@ -9821,13 +9965,13 @@
         <v>27.273</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="I5" s="10"/>
     </row>
@@ -9836,7 +9980,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>6</v>
@@ -9848,13 +9992,13 @@
         <v>27.273</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="I6" s="10"/>
     </row>
@@ -9863,7 +10007,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>6</v>
@@ -9875,13 +10019,13 @@
         <v>27.273</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I7" s="10"/>
     </row>
@@ -9890,7 +10034,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>6</v>
@@ -9902,13 +10046,13 @@
         <v>27.273</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="I8" s="10"/>
     </row>
@@ -9917,7 +10061,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>6</v>
@@ -9929,13 +10073,13 @@
         <v>27.273</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="I9" s="10"/>
     </row>
@@ -9944,7 +10088,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>6</v>
@@ -9956,13 +10100,13 @@
         <v>27.273</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="I10" s="11"/>
     </row>
@@ -9996,7 +10140,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C1" s="3" t="n">
         <v>6</v>
@@ -10008,13 +10152,13 @@
         <v>16.364</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G1" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="11"/>
@@ -10083,7 +10227,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
@@ -10095,13 +10239,13 @@
         <v>16.364</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="G2" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="I2" s="10"/>
       <c r="J2" s="11"/>
@@ -10170,7 +10314,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>6</v>
@@ -10182,13 +10326,13 @@
         <v>16.364</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="11"/>
@@ -10257,7 +10401,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>6</v>
@@ -10269,13 +10413,13 @@
         <v>16.364</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>18</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" s="11"/>
@@ -10344,7 +10488,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>6</v>
@@ -10431,7 +10575,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>6</v>
@@ -10518,7 +10662,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>6</v>
@@ -10605,7 +10749,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>6</v>
@@ -10692,7 +10836,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>6</v>
@@ -10779,7 +10923,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>6</v>
@@ -10866,7 +11010,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>6</v>
@@ -10953,7 +11097,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>6</v>
@@ -11040,7 +11184,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>6</v>
@@ -11058,7 +11202,7 @@
         <v>17.001</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="11"/>
@@ -11127,7 +11271,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>6</v>
@@ -11139,13 +11283,13 @@
         <v>15.455</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>17.001</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="I14" s="10"/>
       <c r="J14" s="11"/>
@@ -11214,7 +11358,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>6</v>
@@ -11301,7 +11445,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>6</v>
@@ -11319,7 +11463,7 @@
         <v>17.001</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="11"/>
@@ -11388,7 +11532,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>6</v>
@@ -11400,13 +11544,13 @@
         <v>15.455</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>17.001</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="11"/>
@@ -11475,7 +11619,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>6</v>
@@ -11487,13 +11631,13 @@
         <v>15.455</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>17.001</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="11"/>
@@ -11562,7 +11706,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>6</v>
@@ -11574,13 +11718,13 @@
         <v>16.955</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>18.651</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="I19" s="10"/>
       <c r="J19" s="11"/>
@@ -11649,7 +11793,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>6</v>
@@ -11661,13 +11805,13 @@
         <v>16.955</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>18.651</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="11"/>
@@ -11736,7 +11880,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>6</v>
@@ -11748,13 +11892,13 @@
         <v>16.955</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>18.651</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="11"/>
@@ -11823,7 +11967,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>6</v>
@@ -11835,13 +11979,13 @@
         <v>16.955</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>18.651</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="11"/>
@@ -11910,7 +12054,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>6</v>
@@ -11922,13 +12066,13 @@
         <v>16.682</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>18.35</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="11"/>
@@ -11997,7 +12141,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>6</v>
@@ -12009,13 +12153,13 @@
         <v>16.682</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>18.35</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="I24" s="10"/>
       <c r="J24" s="11"/>
@@ -12084,7 +12228,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>6</v>
@@ -12096,13 +12240,13 @@
         <v>16.682</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="G25" s="4" t="n">
         <v>18.35</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="11"/>
@@ -12171,7 +12315,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>6</v>
@@ -12183,13 +12327,13 @@
         <v>16.682</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="G26" s="4" t="n">
         <v>18.35</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" s="11"/>
@@ -12258,7 +12402,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>6</v>
@@ -12270,13 +12414,13 @@
         <v>17.409</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="11"/>
@@ -12345,7 +12489,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>6</v>
@@ -12357,13 +12501,13 @@
         <v>17.409</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="G28" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" s="11"/>
@@ -12432,7 +12576,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>6</v>
@@ -12444,13 +12588,13 @@
         <v>17.409</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="I29" s="10"/>
       <c r="J29" s="11"/>
@@ -12519,7 +12663,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>6</v>
@@ -12531,13 +12675,13 @@
         <v>17.409</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>19.15</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="11"/>
